--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
-In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+    <t>Dokumentiert eine "Durchgeführte Abgabe" eines Arzneimittels ("MedicationDispense"-Ressource). 
+Die "Durchgeführte Abgabe" enthält die abgegebene Medikation und deren Dosierung und dient somit der Nachvollziehbarkeit der abgegebenen Arzneimittel in der e-Medikation. 
+Es können Abweichungen zur "Geplanten Abgabe" hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
+Sofern eine zugehörige "Geplanten Abgabe" vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige "Geplante Abgabe", ersichtlich.
+Der aktuelle Status einer "Durchgeführten Abgabe" wird mittels "status"- und "type"-Element dokumentiert. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
